--- a/KRI_GALPON_protein_mes_actual.xlsx
+++ b/KRI_GALPON_protein_mes_actual.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WSVARGAS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PRONACA\pagina mes actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC050F8-BB64-4971-AAA3-CA165BC1D0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0154CE-D16B-4BBA-B937-73F154DEAF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{A56146D7-F8DA-4092-98E5-11206E29A5AB}"/>
   </bookViews>
@@ -7630,9 +7630,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B8B2B6D-C562-4537-A1F5-B51B70194A92}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:U550"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -7699,7 +7721,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46235</v>
       </c>
@@ -7764,7 +7786,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46174</v>
       </c>
@@ -7829,7 +7851,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46204</v>
       </c>
@@ -7894,7 +7916,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46235</v>
       </c>
@@ -7959,7 +7981,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46235</v>
       </c>
@@ -8024,7 +8046,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46174</v>
       </c>
@@ -8089,7 +8111,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46235</v>
       </c>
@@ -8154,7 +8176,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46266</v>
       </c>
@@ -8219,7 +8241,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46235</v>
       </c>
@@ -8284,7 +8306,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46296</v>
       </c>
@@ -8349,7 +8371,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46266</v>
       </c>
@@ -8414,7 +8436,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>112</v>
       </c>
@@ -8479,7 +8501,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46327</v>
       </c>
@@ -8544,7 +8566,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46327</v>
       </c>
@@ -8609,7 +8631,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="16" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46357</v>
       </c>
@@ -8674,7 +8696,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="17" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46357</v>
       </c>
@@ -8739,7 +8761,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="18" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46174</v>
       </c>
@@ -8804,7 +8826,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="19" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46266</v>
       </c>
@@ -8869,7 +8891,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="20" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46296</v>
       </c>
@@ -8934,7 +8956,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="21" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46235</v>
       </c>
@@ -8999,7 +9021,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="22" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46174</v>
       </c>
@@ -9064,7 +9086,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46357</v>
       </c>
@@ -9129,7 +9151,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="24" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46357</v>
       </c>
@@ -9194,7 +9216,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="25" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>196</v>
       </c>
@@ -9259,7 +9281,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="26" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>112</v>
       </c>
@@ -9324,7 +9346,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="27" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>112</v>
       </c>
@@ -9389,7 +9411,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="28" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46327</v>
       </c>
@@ -9454,7 +9476,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="29" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46235</v>
       </c>
@@ -9519,7 +9541,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="30" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46357</v>
       </c>
@@ -9584,7 +9606,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>112</v>
       </c>
@@ -9649,7 +9671,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="32" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>112</v>
       </c>
@@ -9714,7 +9736,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="33" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46266</v>
       </c>
@@ -9779,7 +9801,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="34" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>270</v>
       </c>
@@ -9844,7 +9866,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="35" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>279</v>
       </c>
@@ -9909,7 +9931,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="36" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>112</v>
       </c>
@@ -9974,7 +9996,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="37" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>46357</v>
       </c>
@@ -10039,7 +10061,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="38" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>279</v>
       </c>
@@ -10104,7 +10126,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="39" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>196</v>
       </c>
@@ -10169,7 +10191,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="40" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>279</v>
       </c>
@@ -10234,7 +10256,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="41" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>320</v>
       </c>
@@ -10299,7 +10321,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="42" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>270</v>
       </c>
@@ -10364,7 +10386,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="43" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>196</v>
       </c>
@@ -10429,7 +10451,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="44" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>46357</v>
       </c>
@@ -10494,7 +10516,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="45" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>279</v>
       </c>
@@ -10559,7 +10581,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="46" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>46266</v>
       </c>
@@ -10624,7 +10646,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="47" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>279</v>
       </c>
@@ -10689,7 +10711,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="48" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>364</v>
       </c>
@@ -10754,7 +10776,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="49" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>370</v>
       </c>
@@ -10819,7 +10841,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="50" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>112</v>
       </c>
@@ -10884,7 +10906,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="51" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>270</v>
       </c>
@@ -10949,7 +10971,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="52" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>196</v>
       </c>
@@ -11014,7 +11036,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="53" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>196</v>
       </c>
@@ -11079,7 +11101,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="54" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>370</v>
       </c>
@@ -11144,7 +11166,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="55" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>270</v>
       </c>
@@ -11209,7 +11231,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="56" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>196</v>
       </c>
@@ -11274,7 +11296,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="57" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>112</v>
       </c>
@@ -11339,7 +11361,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="58" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>270</v>
       </c>
@@ -11404,7 +11426,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="59" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>46357</v>
       </c>
@@ -11469,7 +11491,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="60" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>196</v>
       </c>
@@ -11534,7 +11556,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="61" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>270</v>
       </c>
@@ -11599,7 +11621,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="62" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>364</v>
       </c>
@@ -11664,7 +11686,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="63" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>320</v>
       </c>
@@ -11729,7 +11751,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="64" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>320</v>
       </c>
@@ -11794,7 +11816,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="65" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>364</v>
       </c>
@@ -11859,7 +11881,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="66" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>320</v>
       </c>
@@ -11924,7 +11946,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="67" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>320</v>
       </c>
@@ -11989,7 +12011,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="68" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>364</v>
       </c>
@@ -12054,7 +12076,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>491</v>
       </c>
@@ -12119,7 +12141,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="70" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>491</v>
       </c>
@@ -12184,7 +12206,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>491</v>
       </c>
@@ -12249,7 +12271,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>491</v>
       </c>
@@ -12314,7 +12336,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="73" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>364</v>
       </c>
@@ -12379,7 +12401,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>491</v>
       </c>
@@ -12444,7 +12466,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>491</v>
       </c>
@@ -12509,7 +12531,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>534</v>
       </c>
@@ -12574,7 +12596,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>491</v>
       </c>
@@ -12639,7 +12661,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>545</v>
       </c>
@@ -12704,7 +12726,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>364</v>
       </c>
@@ -12769,7 +12791,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="80" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>364</v>
       </c>
@@ -12834,7 +12856,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="81" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>564</v>
       </c>
@@ -12899,7 +12921,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="82" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>491</v>
       </c>
@@ -12964,7 +12986,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="83" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>491</v>
       </c>
@@ -13029,7 +13051,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="84" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>581</v>
       </c>
@@ -13094,7 +13116,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="85" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>364</v>
       </c>
@@ -13159,7 +13181,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="86" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>320</v>
       </c>
@@ -13224,7 +13246,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="87" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>534</v>
       </c>
@@ -13289,7 +13311,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="88" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>564</v>
       </c>
@@ -13354,7 +13376,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="89" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>534</v>
       </c>
@@ -13419,7 +13441,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="90" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>534</v>
       </c>
@@ -13484,7 +13506,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="91" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>581</v>
       </c>
@@ -13549,7 +13571,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="92" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>364</v>
       </c>
@@ -13614,7 +13636,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="93" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>581</v>
       </c>
@@ -13679,7 +13701,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="94" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>642</v>
       </c>
@@ -13744,7 +13766,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="95" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>491</v>
       </c>
@@ -13809,7 +13831,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="96" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>658</v>
       </c>
@@ -13874,7 +13896,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="97" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>667</v>
       </c>
@@ -13939,7 +13961,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="98" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>673</v>
       </c>
@@ -14004,7 +14026,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="99" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>581</v>
       </c>
@@ -14069,7 +14091,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="100" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>364</v>
       </c>
@@ -14134,7 +14156,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="101" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>581</v>
       </c>
@@ -14199,7 +14221,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="102" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>545</v>
       </c>
@@ -14264,7 +14286,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="103" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>534</v>
       </c>
@@ -14329,7 +14351,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="104" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>673</v>
       </c>
@@ -14394,7 +14416,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="105" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>564</v>
       </c>
@@ -14459,7 +14481,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="106" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>667</v>
       </c>
@@ -14524,7 +14546,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="107" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>564</v>
       </c>
@@ -14589,7 +14611,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="108" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>491</v>
       </c>
@@ -14654,7 +14676,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="109" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>745</v>
       </c>
@@ -14719,7 +14741,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="110" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>745</v>
       </c>
@@ -14784,7 +14806,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="111" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>757</v>
       </c>
@@ -14849,7 +14871,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="112" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>564</v>
       </c>
@@ -14914,7 +14936,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="113" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>673</v>
       </c>
@@ -14979,7 +15001,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="114" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>545</v>
       </c>
@@ -15044,7 +15066,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="115" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>658</v>
       </c>
@@ -15109,7 +15131,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="116" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>581</v>
       </c>
@@ -15174,7 +15196,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="117" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>545</v>
       </c>
@@ -15239,7 +15261,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="118" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>745</v>
       </c>
@@ -15304,7 +15326,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="119" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>745</v>
       </c>
@@ -15369,7 +15391,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="120" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>823</v>
       </c>
@@ -15434,7 +15456,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="121" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>545</v>
       </c>
@@ -15499,7 +15521,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="122" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>545</v>
       </c>
@@ -15564,7 +15586,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="123" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>745</v>
       </c>
@@ -15629,7 +15651,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="124" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>545</v>
       </c>
@@ -15694,7 +15716,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="125" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>581</v>
       </c>
@@ -15759,7 +15781,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="126" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>757</v>
       </c>
@@ -15824,7 +15846,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="127" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>545</v>
       </c>
@@ -15889,7 +15911,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="128" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>757</v>
       </c>
@@ -15954,7 +15976,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="129" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>545</v>
       </c>
@@ -16019,7 +16041,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="130" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>745</v>
       </c>
@@ -16084,7 +16106,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="131" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>757</v>
       </c>
@@ -16149,7 +16171,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="132" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>658</v>
       </c>
@@ -16214,7 +16236,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="133" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>745</v>
       </c>
@@ -16279,7 +16301,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="134" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>658</v>
       </c>
@@ -16344,7 +16366,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="135" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>823</v>
       </c>
@@ -16409,7 +16431,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="136" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>823</v>
       </c>
@@ -16474,7 +16496,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="137" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>642</v>
       </c>
@@ -16539,7 +16561,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="138" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>642</v>
       </c>
@@ -16604,7 +16626,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="139" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>757</v>
       </c>
@@ -16669,7 +16691,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="140" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>757</v>
       </c>
@@ -16734,7 +16756,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="141" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>642</v>
       </c>
@@ -16799,7 +16821,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="142" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>46024</v>
       </c>
@@ -16864,7 +16886,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="143" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>46024</v>
       </c>
@@ -16929,7 +16951,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="144" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>658</v>
       </c>
@@ -16994,7 +17016,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="145" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>642</v>
       </c>
@@ -17059,7 +17081,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="146" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>46024</v>
       </c>
@@ -17124,7 +17146,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="147" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>46024</v>
       </c>
@@ -17189,7 +17211,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="148" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>545</v>
       </c>
@@ -17254,7 +17276,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="149" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>545</v>
       </c>
@@ -17319,7 +17341,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="150" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>46055</v>
       </c>
@@ -17384,7 +17406,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="151" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>46024</v>
       </c>
@@ -17449,7 +17471,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="152" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>658</v>
       </c>
@@ -17514,7 +17536,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="153" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>46083</v>
       </c>
@@ -17579,7 +17601,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="154" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>46055</v>
       </c>
@@ -17644,7 +17666,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="155" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>46024</v>
       </c>
@@ -17709,7 +17731,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="156" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>757</v>
       </c>
@@ -17774,7 +17796,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="157" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>46083</v>
       </c>
@@ -17839,7 +17861,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="158" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>745</v>
       </c>
@@ -17904,7 +17926,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="159" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>642</v>
       </c>
@@ -17969,7 +17991,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="160" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>46114</v>
       </c>
@@ -18034,7 +18056,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="161" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>642</v>
       </c>
@@ -18099,7 +18121,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="162" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>46144</v>
       </c>
@@ -18164,7 +18186,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="163" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>46114</v>
       </c>
@@ -18229,7 +18251,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="164" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>46083</v>
       </c>
@@ -18294,7 +18316,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="165" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>46055</v>
       </c>
@@ -18359,7 +18381,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="166" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>46024</v>
       </c>
@@ -18424,7 +18446,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="167" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>46114</v>
       </c>
@@ -18489,7 +18511,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="168" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>46144</v>
       </c>
@@ -18554,7 +18576,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="169" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>46114</v>
       </c>
@@ -18619,7 +18641,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="170" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>46055</v>
       </c>
@@ -18684,7 +18706,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="171" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>46175</v>
       </c>
@@ -18749,7 +18771,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="172" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>46205</v>
       </c>
@@ -18814,7 +18836,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="173" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>46083</v>
       </c>
@@ -18879,7 +18901,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="174" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>46144</v>
       </c>
@@ -18944,7 +18966,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="175" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>46114</v>
       </c>
@@ -19009,7 +19031,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="176" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>46024</v>
       </c>
@@ -19074,7 +19096,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="177" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>46175</v>
       </c>
@@ -19139,7 +19161,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="178" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>658</v>
       </c>
@@ -19204,7 +19226,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="179" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>46114</v>
       </c>
@@ -19269,7 +19291,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="180" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>46205</v>
       </c>
@@ -19334,7 +19356,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="181" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>46083</v>
       </c>
@@ -19399,7 +19421,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="182" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>46083</v>
       </c>
@@ -19464,7 +19486,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="183" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>46024</v>
       </c>
@@ -19529,7 +19551,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="184" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>46267</v>
       </c>
@@ -19594,7 +19616,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="185" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>46055</v>
       </c>
@@ -19659,7 +19681,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="186" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>46144</v>
       </c>
@@ -19724,7 +19746,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="187" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>46114</v>
       </c>
@@ -19789,7 +19811,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="188" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>46267</v>
       </c>
@@ -19854,7 +19876,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="189" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>46236</v>
       </c>
@@ -19919,7 +19941,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="190" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>46144</v>
       </c>
@@ -19984,7 +20006,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="191" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>46236</v>
       </c>
@@ -20049,7 +20071,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="192" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>46114</v>
       </c>
@@ -20114,7 +20136,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="193" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>46055</v>
       </c>
@@ -20179,7 +20201,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="194" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>46175</v>
       </c>
@@ -20244,7 +20266,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="195" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>46114</v>
       </c>
@@ -20309,7 +20331,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="196" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>46083</v>
       </c>
@@ -20374,7 +20396,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="197" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>46175</v>
       </c>
@@ -20439,7 +20461,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="198" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>46267</v>
       </c>
@@ -20504,7 +20526,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="199" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>46144</v>
       </c>
@@ -20569,7 +20591,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="200" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>46236</v>
       </c>
@@ -20634,7 +20656,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="201" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>46144</v>
       </c>
@@ -20699,7 +20721,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="202" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>46114</v>
       </c>
@@ -20764,7 +20786,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="203" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>46083</v>
       </c>
@@ -20829,7 +20851,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="204" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>46328</v>
       </c>
@@ -20894,7 +20916,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="205" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>46205</v>
       </c>
@@ -20959,7 +20981,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="206" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>46205</v>
       </c>
@@ -21024,7 +21046,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="207" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>46144</v>
       </c>
@@ -21089,7 +21111,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="208" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>46205</v>
       </c>
@@ -21154,7 +21176,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="209" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>46114</v>
       </c>
@@ -21219,7 +21241,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="210" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>46297</v>
       </c>
@@ -21284,7 +21306,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="211" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>46236</v>
       </c>
@@ -21349,7 +21371,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="212" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>46328</v>
       </c>
@@ -21414,7 +21436,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="213" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>46328</v>
       </c>
@@ -21479,7 +21501,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="214" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>46267</v>
       </c>
@@ -21544,7 +21566,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="215" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>46297</v>
       </c>
@@ -21609,7 +21631,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="216" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>46328</v>
       </c>
@@ -21674,7 +21696,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="217" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>46236</v>
       </c>
@@ -21739,7 +21761,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="218" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>46297</v>
       </c>
@@ -21804,7 +21826,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="219" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>46267</v>
       </c>
@@ -21869,7 +21891,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="220" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>46297</v>
       </c>
@@ -21934,7 +21956,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="221" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>46328</v>
       </c>
@@ -21999,7 +22021,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="222" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>46358</v>
       </c>
@@ -22064,7 +22086,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="223" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>46267</v>
       </c>
@@ -22129,7 +22151,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="224" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>46297</v>
       </c>
@@ -22194,7 +22216,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="225" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>46236</v>
       </c>
@@ -22259,7 +22281,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="226" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>46358</v>
       </c>
@@ -22324,7 +22346,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="227" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>1432</v>
       </c>
@@ -22389,7 +22411,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="228" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>46328</v>
       </c>
@@ -22454,7 +22476,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="229" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>46267</v>
       </c>
@@ -22519,7 +22541,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="230" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>46328</v>
       </c>
@@ -22584,7 +22606,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="231" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>46358</v>
       </c>
@@ -22649,7 +22671,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="232" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>1460</v>
       </c>
@@ -22714,7 +22736,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="233" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>46358</v>
       </c>
@@ -22779,7 +22801,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="234" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>46358</v>
       </c>
@@ -22844,7 +22866,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="235" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>46328</v>
       </c>
@@ -22909,7 +22931,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="236" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>1480</v>
       </c>
@@ -22974,7 +22996,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="237" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>46297</v>
       </c>
@@ -23039,7 +23061,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="238" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>46358</v>
       </c>
@@ -23104,7 +23126,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="239" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>46358</v>
       </c>
@@ -23169,7 +23191,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="240" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>46267</v>
       </c>
@@ -23234,7 +23256,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="241" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>46328</v>
       </c>
@@ -23299,7 +23321,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="242" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>1480</v>
       </c>
@@ -23364,7 +23386,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="243" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>1521</v>
       </c>
@@ -23429,7 +23451,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="244" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>1432</v>
       </c>
@@ -23494,7 +23516,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="245" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>1521</v>
       </c>
@@ -23559,7 +23581,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="246" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>1460</v>
       </c>
@@ -23624,7 +23646,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="247" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>1480</v>
       </c>
@@ -23689,7 +23711,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="248" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>46328</v>
       </c>
@@ -23754,7 +23776,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="249" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>1480</v>
       </c>
@@ -23819,7 +23841,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="250" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>46358</v>
       </c>
@@ -23884,7 +23906,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="251" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>46328</v>
       </c>
@@ -23949,7 +23971,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="252" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1460</v>
       </c>
@@ -24014,7 +24036,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="253" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>1460</v>
       </c>
@@ -24079,7 +24101,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="254" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>1460</v>
       </c>
@@ -24144,7 +24166,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="255" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>1588</v>
       </c>
@@ -24209,7 +24231,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="256" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>1588</v>
       </c>
@@ -24274,7 +24296,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="257" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>1603</v>
       </c>
@@ -24339,7 +24361,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="258" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>1603</v>
       </c>
@@ -24404,7 +24426,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="259" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>46358</v>
       </c>
@@ -24469,7 +24491,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="260" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>1588</v>
       </c>
@@ -24534,7 +24556,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="261" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>1627</v>
       </c>
@@ -24599,7 +24621,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="262" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>1603</v>
       </c>
@@ -24664,7 +24686,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="263" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>1627</v>
       </c>
@@ -24729,7 +24751,7 @@
         <v>1645</v>
       </c>
     </row>
-    <row r="264" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>1460</v>
       </c>
@@ -24794,7 +24816,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="265" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>1627</v>
       </c>
@@ -24859,7 +24881,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="266" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>1603</v>
       </c>
@@ -24924,7 +24946,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="267" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>1663</v>
       </c>
@@ -24989,7 +25011,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="268" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>1668</v>
       </c>
@@ -25054,7 +25076,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="269" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>1663</v>
       </c>
@@ -25119,7 +25141,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="270" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>1679</v>
       </c>
@@ -25184,7 +25206,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="271" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>1603</v>
       </c>
@@ -25249,7 +25271,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="272" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>1603</v>
       </c>
@@ -25314,7 +25336,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="273" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>1663</v>
       </c>
@@ -25379,7 +25401,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="274" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>1668</v>
       </c>
@@ -25444,7 +25466,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="275" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>1627</v>
       </c>
@@ -25509,7 +25531,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="276" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1603</v>
       </c>
@@ -25574,7 +25596,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="277" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1679</v>
       </c>
@@ -25639,7 +25661,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="278" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1663</v>
       </c>
@@ -25704,7 +25726,7 @@
         <v>1727</v>
       </c>
     </row>
-    <row r="279" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1521</v>
       </c>
@@ -25769,7 +25791,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="280" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>1603</v>
       </c>
@@ -25834,7 +25856,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="281" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>1627</v>
       </c>
@@ -25899,7 +25921,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="282" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>1480</v>
       </c>
@@ -25964,7 +25986,7 @@
         <v>1756</v>
       </c>
     </row>
-    <row r="283" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1668</v>
       </c>
@@ -26029,7 +26051,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="284" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1663</v>
       </c>
@@ -26094,7 +26116,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="285" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1668</v>
       </c>
@@ -26159,7 +26181,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="286" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1663</v>
       </c>
@@ -26224,7 +26246,7 @@
         <v>1779</v>
       </c>
     </row>
-    <row r="287" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>1663</v>
       </c>
@@ -26289,7 +26311,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="288" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>1588</v>
       </c>
@@ -26354,7 +26376,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="289" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>1603</v>
       </c>
@@ -26419,7 +26441,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="290" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1663</v>
       </c>
@@ -26484,7 +26506,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="291" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1668</v>
       </c>
@@ -26549,7 +26571,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="292" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>1668</v>
       </c>
@@ -26614,7 +26636,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="293" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1663</v>
       </c>
@@ -26744,7 +26766,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="295" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1668</v>
       </c>
@@ -26874,7 +26896,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="297" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>1668</v>
       </c>
@@ -26939,7 +26961,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="298" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>1627</v>
       </c>
@@ -27199,7 +27221,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="302" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>1668</v>
       </c>
@@ -27459,7 +27481,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="306" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>1668</v>
       </c>
@@ -27654,7 +27676,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="309" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>1627</v>
       </c>
@@ -27979,7 +28001,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="314" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>1663</v>
       </c>
@@ -28239,7 +28261,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="318" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>1627</v>
       </c>
@@ -28434,7 +28456,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="321" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>1603</v>
       </c>
@@ -28499,7 +28521,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="322" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>1663</v>
       </c>
@@ -28824,7 +28846,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="327" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>1668</v>
       </c>
@@ -43319,7 +43341,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="550" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>2241</v>
       </c>
@@ -43385,13 +43407,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U550" xr:uid="{8B8B2B6D-C562-4537-A1F5-B51B70194A92}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="11/30/1899"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:U550" xr:uid="{8B8B2B6D-C562-4537-A1F5-B51B70194A92}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>